--- a/AI/data/Raw Data/Data.xlsx
+++ b/AI/data/Raw Data/Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\ML\Graduation\data\Raw Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D5EB6F-13A4-445F-A5A8-894637374087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B93BDB3-F3F0-4286-B7CF-3B99F86653FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rooms" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="234">
   <si>
     <t>Room_ID</t>
   </si>
@@ -709,19 +709,22 @@
     <t>D09</t>
   </si>
   <si>
-    <t>D11</t>
-  </si>
-  <si>
-    <t>D13</t>
-  </si>
-  <si>
-    <t>D15</t>
-  </si>
-  <si>
-    <t>D17</t>
-  </si>
-  <si>
-    <t>D19</t>
+    <t>pp</t>
+  </si>
+  <si>
+    <t>D02</t>
+  </si>
+  <si>
+    <t>D04</t>
+  </si>
+  <si>
+    <t>D06</t>
+  </si>
+  <si>
+    <t>D08</t>
+  </si>
+  <si>
+    <t>D10</t>
   </si>
 </sst>
 </file>
@@ -1962,7 +1965,7 @@
         <v>33</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -2979,7 +2982,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" customWidth="1"/>
@@ -3950,7 +3953,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>147</v>
       </c>
@@ -3970,7 +3973,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>147</v>
       </c>
@@ -3990,7 +3993,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>127</v>
       </c>
@@ -4010,7 +4013,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>127</v>
       </c>
@@ -4030,7 +4033,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>140</v>
       </c>
@@ -4050,7 +4053,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>140</v>
       </c>
@@ -4070,7 +4073,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>140</v>
       </c>
@@ -4090,7 +4093,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>140</v>
       </c>
@@ -4110,7 +4113,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>98</v>
       </c>
@@ -4130,7 +4133,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>98</v>
       </c>
@@ -4150,7 +4153,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>98</v>
       </c>
@@ -4170,7 +4173,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>98</v>
       </c>
@@ -4190,7 +4193,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>137</v>
       </c>
@@ -4210,7 +4213,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>137</v>
       </c>
@@ -4230,7 +4233,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>137</v>
       </c>
@@ -4250,7 +4253,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>137</v>
       </c>
@@ -4268,6 +4271,9 @@
       </c>
       <c r="F64" s="1">
         <v>0.375</v>
+      </c>
+      <c r="J64" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -4681,7 +4687,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B3" t="s">
         <v>33</v>
@@ -4698,7 +4704,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B4" t="s">
         <v>33</v>
@@ -4715,7 +4721,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B5" t="s">
         <v>33</v>
@@ -4732,7 +4738,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B6" t="s">
         <v>97</v>
@@ -4749,7 +4755,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B7" t="s">
         <v>97</v>
@@ -4766,7 +4772,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B8" t="s">
         <v>97</v>
@@ -4783,7 +4789,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B9" t="s">
         <v>97</v>
@@ -4800,7 +4806,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B10" t="s">
         <v>97</v>
@@ -4817,7 +4823,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B11" t="s">
         <v>97</v>
